--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.28357</v>
+        <v>17.05969</v>
       </c>
       <c r="D2" t="n">
-        <v>16.94144</v>
+        <v>16.77506</v>
       </c>
       <c r="E2" t="n">
-        <v>17.0247</v>
+        <v>16.98743</v>
       </c>
       <c r="F2" t="n">
-        <v>43.17406</v>
+        <v>43.54111</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05006</v>
+        <v>0.05197</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85811</v>
+        <v>1.85567</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.92045</v>
+        <v>17.08471</v>
       </c>
       <c r="D3" t="n">
-        <v>16.84229</v>
+        <v>16.70605</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63987</v>
+        <v>17.00023</v>
       </c>
       <c r="F3" t="n">
-        <v>42.44708</v>
+        <v>43.8228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05098</v>
+        <v>0.05134</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79061</v>
+        <v>1.8547</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.32721</v>
+        <v>17.29567</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62091</v>
+        <v>16.70573</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73844</v>
+        <v>16.71952</v>
       </c>
       <c r="F4" t="n">
-        <v>42.17247</v>
+        <v>43.2804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05228</v>
+        <v>0.05107</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82309</v>
+        <v>1.80974</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87493</v>
+        <v>17.02752</v>
       </c>
       <c r="D6" t="n">
-        <v>16.14627</v>
+        <v>15.89406</v>
       </c>
       <c r="E6" t="n">
-        <v>16.31523</v>
+        <v>16.5114</v>
       </c>
       <c r="F6" t="n">
-        <v>21.85424</v>
+        <v>21.83727</v>
       </c>
       <c r="G6" t="n">
-        <v>34.73877</v>
+        <v>33.72854</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67794</v>
+        <v>17.01455</v>
       </c>
       <c r="D7" t="n">
-        <v>15.92439</v>
+        <v>16.07789</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67589</v>
+        <v>16.51942</v>
       </c>
       <c r="F7" t="n">
-        <v>21.80977</v>
+        <v>21.85984</v>
       </c>
       <c r="G7" t="n">
-        <v>34.65051</v>
+        <v>34.30383</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.49794</v>
+        <v>16.9608</v>
       </c>
       <c r="D8" t="n">
-        <v>16.19385</v>
+        <v>15.94581</v>
       </c>
       <c r="E8" t="n">
-        <v>16.62585</v>
+        <v>16.59069</v>
       </c>
       <c r="F8" t="n">
-        <v>21.99977</v>
+        <v>21.96421</v>
       </c>
       <c r="G8" t="n">
-        <v>34.87732</v>
+        <v>35.07791</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61277</v>
+        <v>0.61267</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10172</v>
+        <v>1.1164</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.62529</v>
+        <v>0.60146</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10513</v>
+        <v>1.10764</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60531</v>
+        <v>0.61194</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12174</v>
+        <v>1.14695</v>
       </c>
     </row>
   </sheetData>
